--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.80343520985772</v>
+        <v>11.66805822160188</v>
       </c>
       <c r="D2" t="n">
-        <v>68.53278641375587</v>
+        <v>11.13657779223533</v>
       </c>
       <c r="E2" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F2" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.36621462671689</v>
+        <v>9.484509876841495</v>
       </c>
       <c r="D3" t="n">
-        <v>54.96717518625965</v>
+        <v>8.932165967767192</v>
       </c>
       <c r="E3" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F3" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.8603421024371</v>
+        <v>8.75230559164603</v>
       </c>
       <c r="D4" t="n">
-        <v>50.38678294328802</v>
+        <v>8.187852228284303</v>
       </c>
       <c r="E4" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F4" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.38416393241641</v>
+        <v>9.487426639017666</v>
       </c>
       <c r="D5" t="n">
-        <v>55.53779086242758</v>
+        <v>9.024891015144483</v>
       </c>
       <c r="E5" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F5" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.2401498621856</v>
+        <v>7.67652435260516</v>
       </c>
       <c r="D6" t="n">
-        <v>48.2433381677294</v>
+        <v>7.839542452256027</v>
       </c>
       <c r="E6" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F6" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.60367863843675</v>
+        <v>5.948097778745973</v>
       </c>
       <c r="D7" t="n">
-        <v>47.96806337771726</v>
+        <v>7.794810298879056</v>
       </c>
       <c r="E7" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F7" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.56874025423693</v>
+        <v>3.829920291313502</v>
       </c>
       <c r="D8" t="n">
-        <v>32.19218854416341</v>
+        <v>5.231230638426555</v>
       </c>
       <c r="E8" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F8" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.71447623211395</v>
+        <v>5.803602387718517</v>
       </c>
       <c r="D9" t="n">
-        <v>33.34078614010787</v>
+        <v>5.41787774776753</v>
       </c>
       <c r="E9" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F9" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.76266520873685</v>
+        <v>4.998933096419738</v>
       </c>
       <c r="D10" t="n">
-        <v>31.77092830262024</v>
+        <v>5.16277584917579</v>
       </c>
       <c r="E10" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F10" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.2221496475984</v>
+        <v>1.98609931773474</v>
       </c>
       <c r="D11" t="n">
-        <v>13.98265829502495</v>
+        <v>2.272181972941554</v>
       </c>
       <c r="E11" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F11" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.00775152842947</v>
+        <v>5.363759623369789</v>
       </c>
       <c r="D12" t="n">
-        <v>42.90191070947276</v>
+        <v>6.971560490289323</v>
       </c>
       <c r="E12" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F12" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.14674685923348</v>
+        <v>5.873846364625441</v>
       </c>
       <c r="D13" t="n">
-        <v>44.52392562707453</v>
+        <v>7.235137914399612</v>
       </c>
       <c r="E13" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F13" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>45.56980732870047</v>
+        <v>7.405093690913827</v>
       </c>
       <c r="D14" t="n">
-        <v>52.67499514777161</v>
+        <v>8.559686711512887</v>
       </c>
       <c r="E14" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F14" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.16900438311365</v>
+        <v>5.227463212255969</v>
       </c>
       <c r="D15" t="n">
-        <v>38.7010313599967</v>
+        <v>6.288917595999464</v>
       </c>
       <c r="E15" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F15" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>9.480986397691582</v>
+        <v>1.540660289624882</v>
       </c>
       <c r="D16" t="n">
-        <v>19.31320791582797</v>
+        <v>3.138396286322044</v>
       </c>
       <c r="E16" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F16" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>45.67804894603002</v>
+        <v>7.422682953729879</v>
       </c>
       <c r="D17" t="n">
-        <v>39.16886532058331</v>
+        <v>6.364940614594789</v>
       </c>
       <c r="E17" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F17" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>52.92876793680959</v>
+        <v>8.600924789731557</v>
       </c>
       <c r="D18" t="n">
-        <v>42.06388356247039</v>
+        <v>6.835381078901439</v>
       </c>
       <c r="E18" t="n">
-        <v>16.04089129587098</v>
+        <v>2.606644835579035</v>
       </c>
       <c r="F18" t="n">
-        <v>13.09591976202814</v>
+        <v>2.128086961329572</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
